--- a/measurements/36/Filled_2D_sections/coronal/week36_coronal_Batch_Allmarks.xlsx
+++ b/measurements/36/Filled_2D_sections/coronal/week36_coronal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AK32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,122 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +616,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.053837001784652</v>
+        <v>3451.133786848072</v>
       </c>
       <c r="D2" t="n">
-        <v>27.02753817453617</v>
+        <v>527.6805072171347</v>
       </c>
       <c r="E2" t="n">
-        <v>14.1264842283435</v>
+        <v>275.8027873152778</v>
       </c>
       <c r="F2" t="n">
         <v>1.913252989042234</v>
@@ -525,24 +635,60 @@
         <v>0.1557505384296633</v>
       </c>
       <c r="H2" t="n">
+        <v>11</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.763392857142857</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22.88690476190476</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10.00625676406926</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>22.88690476190476</v>
+      </c>
+      <c r="N2" t="n">
+        <v>17.94642857142857</v>
+      </c>
+      <c r="O2" t="n">
+        <v>16.15513392857143</v>
+      </c>
+      <c r="S2" t="n">
         <v>6</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.553734756097561</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.172256097560976</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.7716114075203252</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="n">
+        <v>4.311755952380953</v>
+      </c>
+      <c r="X2" t="n">
+        <v>11.45461309523809</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>8.045944940476192</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.041294642857143</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.763392857142857</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>8.904907792980369</v>
+      <c r="AK2" s="2" t="n">
+        <v>3394.365079365079</v>
       </c>
     </row>
     <row r="3">
@@ -553,17 +699,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.088042831647829</v>
+        <v>3464.172335600907</v>
       </c>
       <c r="D3" t="n">
-        <v>25.6488329608266</v>
+        <v>500.7629292351859</v>
       </c>
       <c r="E3" t="n">
-        <v>14.42508522766392</v>
+        <v>281.632616349629</v>
       </c>
       <c r="F3" t="n">
         <v>1.778071502249301</v>
@@ -572,24 +718,60 @@
         <v>0.1735981172705418</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5286775914634146</v>
+        <v>1.696428571428571</v>
       </c>
       <c r="J3" t="n">
-        <v>1.30907012195122</v>
+        <v>25.55803571428571</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7762798526422764</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>9.846540178571425</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>25.55803571428571</v>
+      </c>
+      <c r="N3" t="n">
+        <v>17.55580357142857</v>
+      </c>
+      <c r="O3" t="n">
+        <v>15.09300595238095</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7</v>
+      </c>
+      <c r="W3" t="n">
+        <v>4.367559523809524</v>
+      </c>
+      <c r="X3" t="n">
+        <v>11.38020833333333</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.913477891156462</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.860863095238095</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.696428571428571</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>27.53659366979831</v>
+      <c r="AK3" s="2" t="n">
+        <v>537.6192097436814</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +782,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9.25461035098156</v>
+        <v>3527.66439909297</v>
       </c>
       <c r="D4" t="n">
-        <v>26.48503468094803</v>
+        <v>517.0887723423185</v>
       </c>
       <c r="E4" t="n">
-        <v>14.05749819046114</v>
+        <v>274.4559170518602</v>
       </c>
       <c r="F4" t="n">
         <v>1.884050370991314</v>
@@ -619,24 +801,60 @@
         <v>0.1657932749609415</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5288681402439025</v>
+        <v>1.73921130952381</v>
       </c>
       <c r="J4" t="n">
-        <v>1.282393292682927</v>
+        <v>25.03720238095238</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8090891768292684</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>9.662078373015872</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>25.03720238095238</v>
+      </c>
+      <c r="N4" t="n">
+        <v>17.99665178571428</v>
+      </c>
+      <c r="O4" t="n">
+        <v>14.94977678571428</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="W4" t="n">
+        <v>4.200148809523809</v>
+      </c>
+      <c r="X4" t="n">
+        <v>10.67336309523809</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>7.478475765306121</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.872767857142857</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.73921130952381</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>14.04689284374074</v>
+      <c r="AK4" s="2" t="n">
+        <v>274.2488602825573</v>
       </c>
     </row>
     <row r="5">
@@ -647,42 +865,81 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.377453896490184</v>
+        <v>3574.489795918367</v>
       </c>
       <c r="D5" t="n">
-        <v>26.42196676207752</v>
+        <v>515.8574463072277</v>
       </c>
       <c r="E5" t="n">
-        <v>14.00871769974871</v>
+        <v>273.503536042713</v>
       </c>
       <c r="F5" t="n">
         <v>1.886108873658827</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1687969199972595</v>
+        <v>0.1687969199972594</v>
       </c>
       <c r="H5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.135416666666667</v>
+      </c>
+      <c r="J5" t="n">
+        <v>24.51636904761905</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9.148923992673991</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>24.51636904761905</v>
+      </c>
+      <c r="N5" t="n">
+        <v>23.28683035714285</v>
+      </c>
+      <c r="O5" t="n">
+        <v>15.44084821428571</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4.205729166666666</v>
+      </c>
+      <c r="X5" t="n">
+        <v>10.23995535714286</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>7.306237599206349</v>
+      </c>
+      <c r="Z5" t="n">
         <v>4</v>
       </c>
-      <c r="I5" t="n">
-        <v>0.524485518292683</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.255716463414634</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.9409536966463415</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="AD5" t="n">
+        <v>2.135416666666667</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>4.081101190476191</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.963634672619047</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AK5" s="2" t="n">
         <v>1.960631248870583</v>
       </c>
     </row>
@@ -694,43 +951,82 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.053539559785841</v>
+        <v>3451.020408163265</v>
       </c>
       <c r="D6" t="n">
-        <v>26.96447016843936</v>
+        <v>526.449179479054</v>
       </c>
       <c r="E6" t="n">
-        <v>14.08015509931053</v>
+        <v>274.8982662246341</v>
       </c>
       <c r="F6" t="n">
         <v>1.915069115237214</v>
       </c>
       <c r="G6" t="n">
-        <v>0.156474828894417</v>
+        <v>0.1564748288944171</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5020960365853658</v>
+        <v>2.689732142857143</v>
       </c>
       <c r="J6" t="n">
-        <v>1.262099847560976</v>
+        <v>24.64099702380952</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8415205792682927</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>9.767330109126982</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>24.64099702380952</v>
+      </c>
+      <c r="N6" t="n">
+        <v>22.50744047619047</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15.34412202380952</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+      <c r="W6" t="n">
+        <v>4.129464285714286</v>
+      </c>
+      <c r="X6" t="n">
+        <v>9.853050595238095</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>7.425905257936507</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.824404761904762</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3.645833333333333</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.689732142857143</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>0.1488428636263858</v>
+      <c r="AK6" s="2" t="n">
+        <v>0.1488428636263859</v>
       </c>
     </row>
     <row r="7">
@@ -741,17 +1037,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8.79327781082689</v>
+        <v>3351.814058956916</v>
       </c>
       <c r="D7" t="n">
-        <v>29.24346039353347</v>
+        <v>570.9437505404154</v>
       </c>
       <c r="E7" t="n">
-        <v>14.16097723274696</v>
+        <v>276.4762221631549</v>
       </c>
       <c r="F7" t="n">
         <v>2.065073611297714</v>
@@ -760,24 +1056,63 @@
         <v>0.129212085191812</v>
       </c>
       <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.590401785714286</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24.765625</v>
+      </c>
+      <c r="K7" t="n">
+        <v>10.12416294642857</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="n">
+        <v>15.3813244047619</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>24.765625</v>
+      </c>
+      <c r="R7" t="n">
+        <v>19.41824776785714</v>
+      </c>
+      <c r="S7" t="n">
         <v>5</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.5378239329268293</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.268483231707317</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.9032393292682928</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="n">
+        <v>4.055059523809524</v>
+      </c>
+      <c r="X7" t="n">
+        <v>10.50037202380952</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7.065104166666667</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.926711309523809</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>2.974330357142857</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.590401785714286</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>5.35</v>
+      <c r="AK7" s="2" t="n">
+        <v>12.1</v>
       </c>
     </row>
     <row r="8">
@@ -788,43 +1123,76 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8.811719214753124</v>
+        <v>3358.843537414966</v>
       </c>
       <c r="D8" t="n">
-        <v>29.02466617560968</v>
+        <v>566.6720539047604</v>
       </c>
       <c r="E8" t="n">
-        <v>14.17873140079219</v>
+        <v>276.8228511583237</v>
       </c>
       <c r="F8" t="n">
         <v>2.047056633993928</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1314425715432909</v>
+        <v>0.1314425715432908</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>0.568407012195122</v>
+        <v>2.905505952380952</v>
       </c>
       <c r="J8" t="n">
-        <v>1.274104420731707</v>
+        <v>24.87537202380952</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8886623475609756</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>11.02881493506493</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>14.41034226190476</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>24.87537202380952</v>
+      </c>
+      <c r="R8" t="n">
+        <v>18.91322544642857</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+      <c r="W8" t="n">
+        <v>4.077380952380953</v>
+      </c>
+      <c r="X8" t="n">
+        <v>11.09747023809524</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>7.126426091269839</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.905505952380952</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.5476371951219512</v>
+      <c r="AK8" s="2" t="n">
+        <v>2.175688244047619</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1203,73 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.876561570493754</v>
+        <v>3383.560090702947</v>
       </c>
       <c r="D9" t="n">
-        <v>29.6337042959725</v>
+        <v>578.562798159463</v>
       </c>
       <c r="E9" t="n">
-        <v>14.178731421145</v>
+        <v>276.822851555688</v>
       </c>
       <c r="F9" t="n">
-        <v>2.090010976001649</v>
+        <v>2.090010976001648</v>
       </c>
       <c r="G9" t="n">
         <v>0.1270231118591832</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5584984756097561</v>
+        <v>4.302455357142857</v>
       </c>
       <c r="J9" t="n">
-        <v>1.258479420731707</v>
+        <v>24.5703125</v>
       </c>
       <c r="K9" t="n">
-        <v>0.832444105691057</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>11.06197296626984</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>13.85974702380952</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>24.5703125</v>
+      </c>
+      <c r="R9" t="n">
+        <v>18.64862351190476</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8</v>
+      </c>
+      <c r="W9" t="n">
+        <v>4.302455357142857</v>
+      </c>
+      <c r="X9" t="n">
+        <v>12.01636904761905</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>7.268647693452381</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.250076219512195</v>
+      <c r="AK9" s="2" t="n">
+        <v>24.40625</v>
       </c>
     </row>
     <row r="10">
@@ -882,17 +1280,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.919988102320048</v>
+        <v>3400.113378684807</v>
       </c>
       <c r="D10" t="n">
-        <v>29.28040475670884</v>
+        <v>571.6650452500297</v>
       </c>
       <c r="E10" t="n">
-        <v>14.03830802149889</v>
+        <v>274.0812518483116</v>
       </c>
       <c r="F10" t="n">
         <v>2.085750270749689</v>
@@ -901,24 +1299,60 @@
         <v>0.1307434640317297</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5085746951219512</v>
+        <v>1.34672619047619</v>
       </c>
       <c r="J10" t="n">
-        <v>1.249333079268293</v>
+        <v>24.39174107142857</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8232977642276423</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>11.12029897186147</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>12.38839285714286</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>24.39174107142857</v>
+      </c>
+      <c r="R10" t="n">
+        <v>17.30282738095238</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>5.465029761904762</v>
+      </c>
+      <c r="X10" t="n">
+        <v>9.929315476190476</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.615792410714286</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.999255952380952</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.34672619047619</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.8434104261941057</v>
+      <c r="AK10" s="2" t="n">
+        <v>10.07382769450292</v>
       </c>
     </row>
     <row r="11">
@@ -929,17 +1363,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.92088042831648</v>
+        <v>3400.453514739229</v>
       </c>
       <c r="D11" t="n">
-        <v>28.73587058811653</v>
+        <v>561.0336638632275</v>
       </c>
       <c r="E11" t="n">
-        <v>13.84217071823958</v>
+        <v>270.2519044989631</v>
       </c>
       <c r="F11" t="n">
         <v>2.075965625120618</v>
@@ -948,16 +1382,60 @@
         <v>0.1357590730617353</v>
       </c>
       <c r="H11" t="n">
+        <v>11</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.171502976190476</v>
+      </c>
+      <c r="J11" t="n">
+        <v>23.54352678571428</v>
+      </c>
+      <c r="K11" t="n">
+        <v>11.06297348484849</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>13.48400297619048</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>23.54352678571428</v>
+      </c>
+      <c r="R11" t="n">
+        <v>18.19056919642857</v>
+      </c>
+      <c r="S11" t="n">
         <v>5</v>
       </c>
-      <c r="I11" t="n">
-        <v>0.6237614329268293</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.205887957317073</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.8701219512195122</v>
+      <c r="W11" t="n">
+        <v>4.574032738095238</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12.1781994047619</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8.411458333333334</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.701636904761905</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3.171502976190476</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="n">
+        <v>3.85</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1446,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.995240928019037</v>
+        <v>3428.798185941043</v>
       </c>
       <c r="D12" t="n">
-        <v>27.28082540267851</v>
+        <v>532.6256388141995</v>
       </c>
       <c r="E12" t="n">
-        <v>13.85054015241018</v>
+        <v>270.4153077375321</v>
       </c>
       <c r="F12" t="n">
         <v>1.969657869114316</v>
@@ -987,16 +1465,63 @@
         <v>0.1518824701757445</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6245236280487805</v>
+        <v>2.676711309523809</v>
       </c>
       <c r="J12" t="n">
-        <v>1.21436737804878</v>
+        <v>23.70907738095238</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8677019817073172</v>
+        <v>10.14245411706349</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>13.33333333333333</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>23.70907738095238</v>
+      </c>
+      <c r="R12" t="n">
+        <v>18.12779017857143</v>
+      </c>
+      <c r="S12" t="n">
+        <v>4</v>
+      </c>
+      <c r="W12" t="n">
+        <v>6.6015625</v>
+      </c>
+      <c r="X12" t="n">
+        <v>12.19308035714286</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.024832589285714</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.676711309523809</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>3.712797619047619</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.274739583333333</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="n">
+        <v>24.5569816468254</v>
       </c>
     </row>
     <row r="13">
@@ -1007,17 +1532,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9.014574657941703</v>
+        <v>3436.167800453515</v>
       </c>
       <c r="D13" t="n">
-        <v>26.96201884455797</v>
+        <v>526.4013202985127</v>
       </c>
       <c r="E13" t="n">
-        <v>13.99197890700364</v>
+        <v>273.1767310414995</v>
       </c>
       <c r="F13" t="n">
         <v>1.926962513577134</v>
@@ -1026,16 +1551,63 @@
         <v>0.1558297192016971</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5305830792682927</v>
+        <v>2.555803571428571</v>
       </c>
       <c r="J13" t="n">
-        <v>1.252286585365854</v>
+        <v>24.44940476190476</v>
       </c>
       <c r="K13" t="n">
-        <v>0.8236788617886179</v>
+        <v>9.68091804029304</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>12.55952380952381</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>24.44940476190476</v>
+      </c>
+      <c r="R13" t="n">
+        <v>17.22581845238095</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="n">
+        <v>10.35900297619048</v>
+      </c>
+      <c r="U13" t="n">
+        <v>7.747395833333333</v>
+      </c>
+      <c r="V13" t="n">
+        <v>7.098214285714286</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.555803571428571</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3.160342261904762</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.903645833333333</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="n">
+        <v>19.20665922619047</v>
       </c>
     </row>
     <row r="14">
@@ -1046,17 +1618,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9.161808447352767</v>
+        <v>3492.290249433107</v>
       </c>
       <c r="D14" t="n">
-        <v>27.34981135624211</v>
+        <v>533.9725074313935</v>
       </c>
       <c r="E14" t="n">
-        <v>14.06096491871811</v>
+        <v>274.5236007940201</v>
       </c>
       <c r="F14" t="n">
         <v>1.945087802604055</v>
@@ -1065,16 +1637,63 @@
         <v>0.1539155154654194</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5411585365853658</v>
+        <v>1.413690476190476</v>
       </c>
       <c r="J14" t="n">
-        <v>1.268387957317073</v>
+        <v>24.76376488095238</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8294270833333334</v>
+        <v>9.354007227891158</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5</v>
+      </c>
+      <c r="P14" t="n">
+        <v>12.32142857142857</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>24.76376488095238</v>
+      </c>
+      <c r="R14" t="n">
+        <v>17.31919642857143</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4</v>
+      </c>
+      <c r="W14" t="n">
+        <v>6.495535714285714</v>
+      </c>
+      <c r="X14" t="n">
+        <v>10.56547619047619</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8.131045386904761</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.413690476190476</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>3.809523809523809</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.3671875</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="n">
+        <v>15.40767609126984</v>
       </c>
     </row>
     <row r="15">
@@ -1085,35 +1704,79 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9.258477096966091</v>
+        <v>3529.138321995465</v>
       </c>
       <c r="D15" t="n">
-        <v>24.28052800748407</v>
+        <v>474.0484039556412</v>
       </c>
       <c r="E15" t="n">
-        <v>14.02055386799138</v>
+        <v>273.7346231369745</v>
       </c>
       <c r="F15" t="n">
         <v>1.73178094361279</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1973481988918808</v>
+        <v>0.1973481988918809</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5521150914634146</v>
+        <v>2.507440476190476</v>
       </c>
       <c r="J15" t="n">
-        <v>1.265243902439025</v>
+        <v>24.70238095238095</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8064786585365853</v>
+        <v>9.615110367063492</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>24.70238095238095</v>
+      </c>
+      <c r="N15" t="n">
+        <v>15.94680059523809</v>
+      </c>
+      <c r="O15" t="n">
+        <v>15.46316964285714</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="W15" t="n">
+        <v>4.272693452380953</v>
+      </c>
+      <c r="X15" t="n">
+        <v>11.8359375</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>7.730654761904761</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.646949404761905</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.507440476190476</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="n">
+        <v>13.76474808673469</v>
       </c>
     </row>
     <row r="16">
@@ -1124,17 +1787,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.941701368233195</v>
+        <v>3408.390022675737</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69820830007879</v>
+        <v>540.7745430015382</v>
       </c>
       <c r="E16" t="n">
-        <v>14.03238999262089</v>
+        <v>273.9657093797411</v>
       </c>
       <c r="F16" t="n">
         <v>1.973876746202482</v>
@@ -1143,16 +1806,63 @@
         <v>0.1464625770531228</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I16" t="n">
-        <v>0.536204268292683</v>
+        <v>1.264880952380952</v>
       </c>
       <c r="J16" t="n">
-        <v>1.253239329268293</v>
+        <v>24.46800595238095</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8196297002032521</v>
+        <v>10.01581101190476</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>15.03162202380952</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>24.46800595238095</v>
+      </c>
+      <c r="R16" t="n">
+        <v>18.47749255952381</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4.990699404761904</v>
+      </c>
+      <c r="X16" t="n">
+        <v>11.63504464285714</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>8.027157738095237</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.784598214285714</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.094494047619047</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.264880952380952</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="n">
+        <v>24.34165072278912</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1873,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.830755502676979</v>
+        <v>3366.09977324263</v>
       </c>
       <c r="D17" t="n">
-        <v>26.72158311925283</v>
+        <v>521.7070989949362</v>
       </c>
       <c r="E17" t="n">
-        <v>14.17873144440535</v>
+        <v>276.8228520098186</v>
       </c>
       <c r="F17" t="n">
         <v>1.884624391401154</v>
@@ -1182,16 +1892,63 @@
         <v>0.1554115729273357</v>
       </c>
       <c r="H17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.731770833333333</v>
+      </c>
+      <c r="J17" t="n">
+        <v>24.34709821428571</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9.817398313492061</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>14.81026785714286</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>24.34709821428571</v>
+      </c>
+      <c r="R17" t="n">
+        <v>18.40494791666667</v>
+      </c>
+      <c r="S17" t="n">
         <v>5</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.5649771341463414</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.247046493902439</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.8671493902439025</v>
+      <c r="W17" t="n">
+        <v>4.1796875</v>
+      </c>
+      <c r="X17" t="n">
+        <v>11.03050595238095</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>7.379836309523808</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.847842261904762</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.710193452380952</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.731770833333333</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="n">
+        <v>18.24895036139456</v>
       </c>
     </row>
     <row r="18">
@@ -1202,17 +1959,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.657644259369423</v>
+        <v>3300.113378684807</v>
       </c>
       <c r="D18" t="n">
-        <v>27.92782321208861</v>
+        <v>545.2575008074442</v>
       </c>
       <c r="E18" t="n">
-        <v>14.07280105207025</v>
+        <v>274.7546872070857</v>
       </c>
       <c r="F18" t="n">
         <v>1.984524836864666</v>
@@ -1221,16 +1978,63 @@
         <v>0.1394875439704923</v>
       </c>
       <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.563244047619047</v>
+      </c>
+      <c r="J18" t="n">
+        <v>24.30245535714285</v>
+      </c>
+      <c r="K18" t="n">
+        <v>10.0523933531746</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>13.88206845238095</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>24.30245535714285</v>
+      </c>
+      <c r="R18" t="n">
+        <v>18.23149181547619</v>
+      </c>
+      <c r="S18" t="n">
         <v>5</v>
       </c>
-      <c r="I18" t="n">
-        <v>0.5453506097560976</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.244759908536585</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.8561166158536586</v>
+      <c r="W18" t="n">
+        <v>4.791666666666666</v>
+      </c>
+      <c r="X18" t="n">
+        <v>10.64732142857143</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>7.731398809523808</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.249627976190476</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.232886904761905</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.563244047619047</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AK18" s="2" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="19">
@@ -1241,17 +2045,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8.530933967876264</v>
+        <v>3251.814058956916</v>
       </c>
       <c r="D19" t="n">
-        <v>28.78913314749555</v>
+        <v>562.073551927294</v>
       </c>
       <c r="E19" t="n">
-        <v>13.99544560909271</v>
+        <v>273.2444142727625</v>
       </c>
       <c r="F19" t="n">
         <v>2.057035835199954</v>
@@ -1260,16 +2064,60 @@
         <v>0.1293448876222735</v>
       </c>
       <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.107514880952381</v>
+      </c>
+      <c r="J19" t="n">
+        <v>24.19270833333333</v>
+      </c>
+      <c r="K19" t="n">
+        <v>10.38922991071428</v>
+      </c>
+      <c r="L19" t="n">
+        <v>4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>12.85342261904762</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>24.19270833333333</v>
+      </c>
+      <c r="R19" t="n">
+        <v>18.20265997023809</v>
+      </c>
+      <c r="S19" t="n">
         <v>6</v>
       </c>
-      <c r="I19" t="n">
-        <v>0.5142911585365854</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1.239138719512195</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.8020674542682927</v>
+      <c r="W19" t="n">
+        <v>3.839285714285714</v>
+      </c>
+      <c r="X19" t="n">
+        <v>11.10491071428571</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>7.670820932539683</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>3.727678571428571</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.107514880952381</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="n">
+        <v>10.35900297619048</v>
       </c>
     </row>
     <row r="20">
@@ -1280,35 +2128,82 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.347412254610351</v>
+        <v>3181.859410430839</v>
       </c>
       <c r="D20" t="n">
-        <v>27.62922220986064</v>
+        <v>539.4276717163267</v>
       </c>
       <c r="E20" t="n">
-        <v>13.86930968703293</v>
+        <v>270.7817605563573</v>
       </c>
       <c r="F20" t="n">
         <v>1.992112284845185</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1374119200627328</v>
+        <v>0.1374119200627329</v>
       </c>
       <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.956845238095238</v>
+      </c>
+      <c r="J20" t="n">
+        <v>24.21130952380952</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10.26134672619048</v>
+      </c>
+      <c r="L20" t="n">
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>14.15550595238095</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>24.21130952380952</v>
+      </c>
+      <c r="R20" t="n">
+        <v>18.54864211309524</v>
+      </c>
+      <c r="S20" t="n">
         <v>5</v>
       </c>
-      <c r="I20" t="n">
-        <v>0.5581173780487805</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.240091463414634</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.8716653963414636</v>
+      <c r="W20" t="n">
+        <v>4.259672619047619</v>
+      </c>
+      <c r="X20" t="n">
+        <v>10.89657738095238</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>8.032738095238095</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>3.537946428571428</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.283110119047619</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.956845238095238</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="n">
+        <v>7.747395833333333</v>
       </c>
     </row>
     <row r="21">
@@ -1319,17 +2214,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>coronal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8.209696609161213</v>
+        <v>3129.365079365079</v>
       </c>
       <c r="D21" t="n">
-        <v>27.62677083945856</v>
+        <v>539.3798116275242</v>
       </c>
       <c r="E21" t="n">
-        <v>13.76828200351901</v>
+        <v>268.8093153067998</v>
       </c>
       <c r="F21" t="n">
         <v>2.006551785647438</v>
@@ -1338,16 +2233,63 @@
         <v>0.1351688819164438</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5504954268292683</v>
+        <v>1.395089285714286</v>
       </c>
       <c r="J21" t="n">
-        <v>1.239138719512195</v>
+        <v>24.19270833333333</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8670731707317072</v>
+        <v>9.318532100340134</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>14.23549107142857</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>24.19270833333333</v>
+      </c>
+      <c r="R21" t="n">
+        <v>18.47377232142857</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6</v>
+      </c>
+      <c r="W21" t="n">
+        <v>4.135044642857142</v>
+      </c>
+      <c r="X21" t="n">
+        <v>10.74776785714286</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>7.840401785714285</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.395089285714286</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>3.407738095238095</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.380487351190476</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>Secondary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK21" s="2" t="n">
+        <v>7.098214285714286</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2299,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="n">
+        <v>4.59234022556391</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2321,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="n">
+        <v>11.0515546679198</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2338,120 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="n">
+        <v>7.748755608328857</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AK25" s="2" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="n">
+        <v>3.351934523809523</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AK27" s="2" t="n">
+        <v>2.482543498168498</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>Tertiary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="n">
+        <v>1.966145833333333</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="n">
+        <v>2.035342261904762</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="n">
+        <v>3.634300595238095</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="n">
+        <v>2.777938988095238</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/measurements/36/Filled_2D_sections/coronal/week36_coronal_Batch_Allmarks.xlsx
+++ b/measurements/36/Filled_2D_sections/coronal/week36_coronal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2457,4 +2663,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week36_coronal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coronal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3394.365079365079</v>
+      </c>
+      <c r="D10" t="n">
+        <v>112.6354509102339</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3129.365079365079</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3574.489795918367</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>537.6192097436814</v>
+      </c>
+      <c r="D11" t="n">
+        <v>26.10357341936888</v>
+      </c>
+      <c r="E11" t="n">
+        <v>474.0484039556412</v>
+      </c>
+      <c r="F11" t="n">
+        <v>578.562798159463</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.960631248870583</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0989115631521056</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.73178094361279</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.090010976001648</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1488428636263858</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.01826412218481826</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.1270231118591832</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1973481988918809</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis1_s00_idx0138.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis1_s01_idx0139.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis1_s02_idx0141.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis1_s03_idx0143.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis1_s04_idx0145.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>12</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>12</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis1_s05_idx0146.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>12</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis1_s06_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>11</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>11</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis1_s07_idx0150.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>12</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>12</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis1_s08_idx0152.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>11</v>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>11</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis1_s09_idx0154.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>11</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>11</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis1_s10_idx0155.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>12</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>12</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis1_s11_idx0157.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>13</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>13</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis1_s12_idx0159.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>14</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>14</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis1_s13_idx0161.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>12</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>12</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis1_s14_idx0163.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>12</v>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>5</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>12</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis1_s15_idx0164.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>12</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="n">
+        <v>5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>12</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis1_s16_idx0166.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>12</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>12</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis1_s17_idx0168.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>12</v>
+      </c>
+      <c r="C34" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>12</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis1_s18_idx0170.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>12</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>12</v>
+      </c>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis1_s19_idx0172.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>14</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>14</v>
+      </c>
+      <c r="H36" t="n">
+        <v>4</v>
+      </c>
+      <c r="I36" t="n">
+        <v>6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.8522416262267903</v>
+      </c>
+      <c r="E40" t="n">
+        <v>11</v>
+      </c>
+      <c r="F40" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.670820393249937</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.235441536242684</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.25131509768092</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>77</v>
+      </c>
+      <c r="C48" t="n">
+        <v>18.55606447124304</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3.950820322649803</v>
+      </c>
+      <c r="E48" t="n">
+        <v>12.32142857142857</v>
+      </c>
+      <c r="F48" t="n">
+        <v>25.55803571428571</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>110</v>
+      </c>
+      <c r="C49" t="n">
+        <v>7.72756020021645</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.008319274540344</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.839285714285714</v>
+      </c>
+      <c r="F49" t="n">
+        <v>12.19308035714286</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>55</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2.760484307359307</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.7639350952360339</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.264880952380952</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.081101190476191</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>